--- a/data/trans_orig/P57_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57_R2-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2016</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75110</t>
+          <t>76465</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109207</t>
+          <t>109255</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59801</t>
+          <t>59161</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89647</t>
+          <t>89848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144323</t>
+          <t>141889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>188647</t>
+          <t>185174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>183624</t>
+          <t>183576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>217721</t>
+          <t>216366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199056</t>
+          <t>198855</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228902</t>
+          <t>229542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>392887</t>
+          <t>396360</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>437211</t>
+          <t>439645</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,6%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>152780</t>
+          <t>155448</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195248</t>
+          <t>197208</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145018</t>
+          <t>146978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>189207</t>
+          <t>187656</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>312185</t>
+          <t>313331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>369588</t>
+          <t>372590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>304121</t>
+          <t>302161</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>346589</t>
+          <t>343921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331966</t>
+          <t>333517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376155</t>
+          <t>374195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>650954</t>
+          <t>647952</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>708357</t>
+          <t>707211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81098</t>
+          <t>80636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111988</t>
+          <t>113537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81703</t>
+          <t>79300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114060</t>
+          <t>112604</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170207</t>
+          <t>173959</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215186</t>
+          <t>217388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>205712</t>
+          <t>204163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>236602</t>
+          <t>237064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222249</t>
+          <t>223705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254606</t>
+          <t>257009</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>438823</t>
+          <t>436621</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>483802</t>
+          <t>480050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,4%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130310</t>
+          <t>131079</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167967</t>
+          <t>169820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114795</t>
+          <t>116445</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>153179</t>
+          <t>155840</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>257044</t>
+          <t>256485</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>310614</t>
+          <t>310108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198973</t>
+          <t>197120</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>236630</t>
+          <t>235861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231694</t>
+          <t>229033</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>270078</t>
+          <t>268428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>441199</t>
+          <t>441705</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>494769</t>
+          <t>495328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,88%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>23733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43960</t>
+          <t>44669</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17229</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35739</t>
+          <t>36748</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45526</t>
+          <t>45135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72254</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167261</t>
+          <t>166552</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188403</t>
+          <t>187488</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182848</t>
+          <t>181839</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201358</t>
+          <t>201374</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>357554</t>
+          <t>355565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384282</t>
+          <t>384673</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119417</t>
+          <t>118815</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>150711</t>
+          <t>150714</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107034</t>
+          <t>105831</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>138484</t>
+          <t>138593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>235175</t>
+          <t>234621</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>280964</t>
+          <t>281272</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112412</t>
+          <t>112409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>143706</t>
+          <t>144308</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133629</t>
+          <t>133520</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>165079</t>
+          <t>166282</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>254272</t>
+          <t>253964</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>300061</t>
+          <t>300615</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,17%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>164291</t>
+          <t>167918</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>214770</t>
+          <t>218439</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>152960</t>
+          <t>154068</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>199505</t>
+          <t>202475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>333191</t>
+          <t>334891</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>402461</t>
+          <t>400613</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>436196</t>
+          <t>432527</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>486675</t>
+          <t>483048</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>482687</t>
+          <t>479717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>529232</t>
+          <t>528124</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>930697</t>
+          <t>932545</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>999967</t>
+          <t>998267</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,88%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134154</t>
+          <t>133959</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>179817</t>
+          <t>183022</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111643</t>
+          <t>110743</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>155809</t>
+          <t>157306</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>255758</t>
+          <t>255822</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>317612</t>
+          <t>323913</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>598766</t>
+          <t>595561</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>644429</t>
+          <t>644624</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>668345</t>
+          <t>666848</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>712511</t>
+          <t>713411</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1285125</t>
+          <t>1278824</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1346979</t>
+          <t>1346915</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>977133</t>
+          <t>977737</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1087918</t>
+          <t>1087075</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>877663</t>
+          <t>877838</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>981482</t>
+          <t>976656</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1875864</t>
+          <t>1880581</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2028846</t>
+          <t>2033723</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2292815</t>
+          <t>2293658</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2403600</t>
+          <t>2402996</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2546622</t>
+          <t>2551448</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2650441</t>
+          <t>2650266</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4879991</t>
+          <t>4875114</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5032973</t>
+          <t>5028256</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2023</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59714</t>
+          <t>59348</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106144</t>
+          <t>106358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38714</t>
+          <t>38830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60801</t>
+          <t>58327</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103074</t>
+          <t>104605</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156153</t>
+          <t>156847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>205299</t>
+          <t>205085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251729</t>
+          <t>252095</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228834</t>
+          <t>231308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250921</t>
+          <t>250805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>444924</t>
+          <t>444230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>498003</t>
+          <t>496472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,6%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>345545</t>
+          <t>350128</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>401959</t>
+          <t>405169</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>327240</t>
+          <t>328434</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>365006</t>
+          <t>365123</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>689198</t>
+          <t>692270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>754058</t>
+          <t>754677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116431</t>
+          <t>113221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172845</t>
+          <t>168262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146231</t>
+          <t>146114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183997</t>
+          <t>182803</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>275568</t>
+          <t>274949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>340428</t>
+          <t>337356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133236</t>
+          <t>133450</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>169307</t>
+          <t>169460</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118722</t>
+          <t>119592</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150894</t>
+          <t>150661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263005</t>
+          <t>263542</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>312089</t>
+          <t>309015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,69%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144996</t>
+          <t>144843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181067</t>
+          <t>180853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>196664</t>
+          <t>196897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>228836</t>
+          <t>227966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>349772</t>
+          <t>352846</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>398856</t>
+          <t>398319</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,18%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100462</t>
+          <t>103676</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>148002</t>
+          <t>146194</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92379</t>
+          <t>90758</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>190609</t>
+          <t>191870</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199866</t>
+          <t>199586</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>321970</t>
+          <t>323680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157498</t>
+          <t>159306</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205038</t>
+          <t>201824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>274363</t>
+          <t>273102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>372593</t>
+          <t>374214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>448502</t>
+          <t>446792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>570606</t>
+          <t>570886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61092</t>
+          <t>61263</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83253</t>
+          <t>83982</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65076</t>
+          <t>65143</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84817</t>
+          <t>85447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131544</t>
+          <t>130882</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162229</t>
+          <t>160336</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95489</t>
+          <t>94760</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117650</t>
+          <t>117479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121891</t>
+          <t>121261</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141632</t>
+          <t>141565</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>223221</t>
+          <t>225114</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>253906</t>
+          <t>254568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,04%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120461</t>
+          <t>121203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149822</t>
+          <t>150571</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>120023</t>
+          <t>121080</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147317</t>
+          <t>145068</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>247846</t>
+          <t>250854</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>288717</t>
+          <t>290526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119814</t>
+          <t>119065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149175</t>
+          <t>148433</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109423</t>
+          <t>111672</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>136717</t>
+          <t>135660</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>237659</t>
+          <t>235850</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>278530</t>
+          <t>275522</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>249438</t>
+          <t>248984</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>310386</t>
+          <t>308523</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108014</t>
+          <t>125589</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>346955</t>
+          <t>344202</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>291951</t>
+          <t>341078</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>631180</t>
+          <t>635691</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,22%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>313134</t>
+          <t>314997</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>374082</t>
+          <t>374536</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>500423</t>
+          <t>503176</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>739364</t>
+          <t>721789</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>839718</t>
+          <t>835207</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1178947</t>
+          <t>1129820</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>374649</t>
+          <t>374026</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>753612</t>
+          <t>758517</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>213635</t>
+          <t>215928</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>260629</t>
+          <t>264074</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>604398</t>
+          <t>600644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1086292</t>
+          <t>1101666</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>174488</t>
+          <t>169583</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>553451</t>
+          <t>554074</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>455459</t>
+          <t>452014</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>502453</t>
+          <t>500160</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>557897</t>
+          <t>542523</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1039791</t>
+          <t>1043545</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,47%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1597551</t>
+          <t>1598032</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2146360</t>
+          <t>2134364</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1122807</t>
+          <t>1098223</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1496713</t>
+          <t>1489538</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2883072</t>
+          <t>2875021</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3555898</t>
+          <t>3560702</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1303273</t>
+          <t>1315269</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1852082</t>
+          <t>1851601</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2143603</t>
+          <t>2150778</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2517509</t>
+          <t>2542093</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3534051</t>
+          <t>3529247</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4206877</t>
+          <t>4214928</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57_R2-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>74348</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109255</t>
+          <t>108149</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59161</t>
+          <t>58460</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89848</t>
+          <t>89516</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141889</t>
+          <t>144994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>185174</t>
+          <t>188331</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>183576</t>
+          <t>184682</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>216366</t>
+          <t>218483</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198855</t>
+          <t>199187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229542</t>
+          <t>230243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>396360</t>
+          <t>393203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>439645</t>
+          <t>436540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>155448</t>
+          <t>154531</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>197208</t>
+          <t>197942</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>146978</t>
+          <t>147191</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187656</t>
+          <t>190805</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>313331</t>
+          <t>310977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>372590</t>
+          <t>368793</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>302161</t>
+          <t>301427</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>343921</t>
+          <t>344838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333517</t>
+          <t>330368</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374195</t>
+          <t>373982</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>647952</t>
+          <t>651749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>707211</t>
+          <t>709565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80636</t>
+          <t>82497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113537</t>
+          <t>114064</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79300</t>
+          <t>82247</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112604</t>
+          <t>113066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>173959</t>
+          <t>172554</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217388</t>
+          <t>218144</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>204163</t>
+          <t>203636</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>237064</t>
+          <t>235203</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>223705</t>
+          <t>223243</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257009</t>
+          <t>254062</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>436621</t>
+          <t>435865</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>480050</t>
+          <t>481455</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131079</t>
+          <t>130263</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169820</t>
+          <t>165676</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116445</t>
+          <t>118011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>155840</t>
+          <t>153730</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>256485</t>
+          <t>257335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>310108</t>
+          <t>309189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197120</t>
+          <t>201264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235861</t>
+          <t>236677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>229033</t>
+          <t>231143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268428</t>
+          <t>266862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>441705</t>
+          <t>442624</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>495328</t>
+          <t>494478</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23733</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44669</t>
+          <t>44112</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17213</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36748</t>
+          <t>35513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45135</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>73900</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166552</t>
+          <t>167109</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187488</t>
+          <t>188931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181839</t>
+          <t>183074</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201374</t>
+          <t>201101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355565</t>
+          <t>355908</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384673</t>
+          <t>384136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118815</t>
+          <t>119084</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>150714</t>
+          <t>150573</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105831</t>
+          <t>106550</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>138593</t>
+          <t>138818</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>234621</t>
+          <t>235697</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>281272</t>
+          <t>279730</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,26%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112409</t>
+          <t>112550</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>144308</t>
+          <t>144039</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133520</t>
+          <t>133295</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166282</t>
+          <t>165563</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>253964</t>
+          <t>255506</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>300615</t>
+          <t>299539</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,96%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167918</t>
+          <t>166432</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>218439</t>
+          <t>217299</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>154068</t>
+          <t>154530</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>202475</t>
+          <t>202066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>334891</t>
+          <t>335914</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>400613</t>
+          <t>406558</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>432527</t>
+          <t>433667</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>483048</t>
+          <t>484534</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>479717</t>
+          <t>480126</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>528124</t>
+          <t>527662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>932545</t>
+          <t>926600</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>998267</t>
+          <t>997244</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,8%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133959</t>
+          <t>131543</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>183022</t>
+          <t>178313</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110743</t>
+          <t>111565</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>157306</t>
+          <t>158118</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>255822</t>
+          <t>259260</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>323913</t>
+          <t>321139</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>595561</t>
+          <t>600270</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>644624</t>
+          <t>647040</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>666848</t>
+          <t>666036</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>713411</t>
+          <t>712589</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1278824</t>
+          <t>1281598</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1346915</t>
+          <t>1343477</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,82%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>977737</t>
+          <t>974570</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1087075</t>
+          <t>1080195</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>877838</t>
+          <t>877364</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>976656</t>
+          <t>988351</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1880581</t>
+          <t>1881644</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2033723</t>
+          <t>2035801</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2293658</t>
+          <t>2300538</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2402996</t>
+          <t>2406163</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2551448</t>
+          <t>2539753</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2650266</t>
+          <t>2650740</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4875114</t>
+          <t>4873036</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5028256</t>
+          <t>5027193</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,76%</t>
         </is>
       </c>
     </row>
@@ -4049,32 +4049,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>79287</t>
+          <t>74292</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59348</t>
+          <t>60256</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106358</t>
+          <t>91544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>48153</t>
+          <t>58333</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38830</t>
+          <t>47255</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58327</t>
+          <t>72717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4119,32 +4119,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>127439</t>
+          <t>132625</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104605</t>
+          <t>113680</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156847</t>
+          <t>154046</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -4162,32 +4162,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>232156</t>
+          <t>244553</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>205085</t>
+          <t>227301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>252095</t>
+          <t>258589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>241482</t>
+          <t>257728</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231308</t>
+          <t>243344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250805</t>
+          <t>268806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4232,32 +4232,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>473638</t>
+          <t>502281</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>444230</t>
+          <t>480860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>496472</t>
+          <t>521226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -4275,17 +4275,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>377911</t>
+          <t>387517</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>350128</t>
+          <t>360461</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>405169</t>
+          <t>412586</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>346851</t>
+          <t>370494</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>328434</t>
+          <t>351833</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>365123</t>
+          <t>389548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>724761</t>
+          <t>758010</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>692270</t>
+          <t>726343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>754677</t>
+          <t>788415</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>140479</t>
+          <t>143130</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113221</t>
+          <t>118061</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>168262</t>
+          <t>170186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>164386</t>
+          <t>172144</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146114</t>
+          <t>153090</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182803</t>
+          <t>190805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>304865</t>
+          <t>315275</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>274949</t>
+          <t>284870</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>337356</t>
+          <t>346942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511237</t>
+          <t>542638</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511237</t>
+          <t>542638</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511237</t>
+          <t>542638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4688,17 +4688,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1029626</t>
+          <t>1073285</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1029626</t>
+          <t>1073285</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1029626</t>
+          <t>1073285</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>151302</t>
+          <t>148938</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133450</t>
+          <t>130659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>169460</t>
+          <t>164467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>134552</t>
+          <t>138144</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119592</t>
+          <t>123589</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150661</t>
+          <t>154908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4805,32 +4805,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>285854</t>
+          <t>287081</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263542</t>
+          <t>263263</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309015</t>
+          <t>310656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>163001</t>
+          <t>165353</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144843</t>
+          <t>149824</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180853</t>
+          <t>183632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>213006</t>
+          <t>216609</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>196897</t>
+          <t>199845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>227966</t>
+          <t>231164</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>376007</t>
+          <t>381963</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>352846</t>
+          <t>358388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>398319</t>
+          <t>405781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,65%</t>
         </is>
       </c>
     </row>
@@ -4961,17 +4961,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314303</t>
+          <t>314291</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314303</t>
+          <t>314291</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314303</t>
+          <t>314291</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>347558</t>
+          <t>354753</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>347558</t>
+          <t>354753</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347558</t>
+          <t>354753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>661861</t>
+          <t>669044</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>661861</t>
+          <t>669044</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>661861</t>
+          <t>669044</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>123748</t>
+          <t>155158</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103676</t>
+          <t>128598</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146194</t>
+          <t>182489</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>150976</t>
+          <t>168107</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90758</t>
+          <t>147009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>191870</t>
+          <t>188247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5148,32 +5148,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>274724</t>
+          <t>323265</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199586</t>
+          <t>293995</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>323680</t>
+          <t>356564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>181752</t>
+          <t>210208</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159306</t>
+          <t>182877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>201824</t>
+          <t>236768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>313996</t>
+          <t>241782</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>273102</t>
+          <t>221642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>374214</t>
+          <t>262880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>495748</t>
+          <t>451989</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>446792</t>
+          <t>418690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>570886</t>
+          <t>481259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>62,08%</t>
         </is>
       </c>
     </row>
@@ -5304,17 +5304,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>305500</t>
+          <t>365366</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>305500</t>
+          <t>365366</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>305500</t>
+          <t>365366</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>464972</t>
+          <t>409889</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>464972</t>
+          <t>409889</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>464972</t>
+          <t>409889</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>770472</t>
+          <t>775254</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>770472</t>
+          <t>775254</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>770472</t>
+          <t>775254</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5421,32 +5421,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>71973</t>
+          <t>83706</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61263</t>
+          <t>71697</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83982</t>
+          <t>95586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5456,32 +5456,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>74388</t>
+          <t>80648</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65143</t>
+          <t>70153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85447</t>
+          <t>91377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5491,32 +5491,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>146361</t>
+          <t>164354</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130882</t>
+          <t>147706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160336</t>
+          <t>180508</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -5534,32 +5534,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>106769</t>
+          <t>121959</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94760</t>
+          <t>110079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117479</t>
+          <t>133968</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>132320</t>
+          <t>145743</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121261</t>
+          <t>135014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141565</t>
+          <t>156238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5604,32 +5604,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>239089</t>
+          <t>267702</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225114</t>
+          <t>251548</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>254568</t>
+          <t>284350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5647,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>206708</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>206708</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>206708</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5717,17 +5717,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>385450</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385450</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>385450</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5764,32 +5764,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>135460</t>
+          <t>133138</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121203</t>
+          <t>118287</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>150571</t>
+          <t>147328</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>133624</t>
+          <t>135785</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>121080</t>
+          <t>122813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145068</t>
+          <t>147924</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5834,32 +5834,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>269084</t>
+          <t>268923</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>250854</t>
+          <t>248590</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>290526</t>
+          <t>286763</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -5877,32 +5877,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>134176</t>
+          <t>137569</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119065</t>
+          <t>123379</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148433</t>
+          <t>152420</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5912,32 +5912,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>123116</t>
+          <t>127652</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>111672</t>
+          <t>115513</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>135660</t>
+          <t>140624</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5947,32 +5947,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>257292</t>
+          <t>265222</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235850</t>
+          <t>247382</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>275522</t>
+          <t>285555</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>53,46%</t>
         </is>
       </c>
     </row>
@@ -5990,17 +5990,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6025,17 +6025,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256740</t>
+          <t>263437</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256740</t>
+          <t>263437</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256740</t>
+          <t>263437</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526376</t>
+          <t>534145</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526376</t>
+          <t>534145</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526376</t>
+          <t>534145</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6107,32 +6107,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>278005</t>
+          <t>317626</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>248984</t>
+          <t>286878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>308523</t>
+          <t>346593</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6142,32 +6142,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>254352</t>
+          <t>303921</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125589</t>
+          <t>280853</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>344202</t>
+          <t>329353</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>532357</t>
+          <t>621547</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>341078</t>
+          <t>578466</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>635691</t>
+          <t>659844</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -6220,32 +6220,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>345515</t>
+          <t>401242</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>314997</t>
+          <t>372275</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>374536</t>
+          <t>431990</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6255,32 +6255,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>593026</t>
+          <t>466098</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>503176</t>
+          <t>440666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>721789</t>
+          <t>489166</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>938541</t>
+          <t>867340</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>835207</t>
+          <t>829043</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1129820</t>
+          <t>910421</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -6333,17 +6333,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623520</t>
+          <t>718868</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623520</t>
+          <t>718868</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623520</t>
+          <t>718868</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847378</t>
+          <t>770019</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847378</t>
+          <t>770019</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847378</t>
+          <t>770019</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6403,17 +6403,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1470898</t>
+          <t>1488887</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1470898</t>
+          <t>1488887</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1470898</t>
+          <t>1488887</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6450,32 +6450,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>529459</t>
+          <t>334011</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>374026</t>
+          <t>304079</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>758517</t>
+          <t>364776</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6485,32 +6485,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>275644</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>215928</t>
+          <t>250436</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>264074</t>
+          <t>301501</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6520,32 +6520,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>767948</t>
+          <t>609655</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>600644</t>
+          <t>567755</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1101666</t>
+          <t>650364</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -6563,32 +6563,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>398641</t>
+          <t>463394</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>169583</t>
+          <t>432629</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>554074</t>
+          <t>493326</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6598,32 +6598,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>477599</t>
+          <t>553886</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>452014</t>
+          <t>528029</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>500160</t>
+          <t>579094</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6633,32 +6633,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>876241</t>
+          <t>1017280</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>542523</t>
+          <t>976571</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1043545</t>
+          <t>1059180</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>65,1%</t>
         </is>
       </c>
     </row>
@@ -6676,17 +6676,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797405</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797405</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797405</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>716088</t>
+          <t>829530</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>716088</t>
+          <t>829530</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>716088</t>
+          <t>829530</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6746,17 +6746,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644189</t>
+          <t>1626935</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644189</t>
+          <t>1626935</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644189</t>
+          <t>1626935</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1747144</t>
+          <t>1634384</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1598032</t>
+          <t>1564810</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2134364</t>
+          <t>1698228</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1381383</t>
+          <t>1531076</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1098223</t>
+          <t>1472474</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1489538</t>
+          <t>1587964</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6863,32 +6863,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3128528</t>
+          <t>3165460</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2875021</t>
+          <t>3077618</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3560702</t>
+          <t>3250344</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -6906,32 +6906,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1702489</t>
+          <t>1887409</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1315269</t>
+          <t>1823565</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1851601</t>
+          <t>1956983</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2258933</t>
+          <t>2181642</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2150778</t>
+          <t>2124754</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2542093</t>
+          <t>2240244</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6976,32 +6976,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3961421</t>
+          <t>4069051</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3529247</t>
+          <t>3984167</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4214928</t>
+          <t>4156893</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>57,46%</t>
         </is>
       </c>
     </row>
@@ -7019,17 +7019,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7089,17 +7089,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
